--- a/Task4_交付物/metadata_filter_test.xlsx
+++ b/Task4_交付物/metadata_filter_test.xlsx
@@ -618,10 +618,10 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>5</v>
@@ -774,10 +774,10 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>5</v>
@@ -855,7 +855,7 @@
         <v>978</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>5</v>
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>5</v>
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>5</v>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1468,10 +1468,10 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1612,10 +1612,10 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>5</v>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>5</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>5</v>
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>5</v>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>5</v>
@@ -2079,7 +2079,7 @@
         <v>847</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>5</v>
@@ -2154,7 +2154,7 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>1190</v>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>5</v>
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>5</v>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>5</v>
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>5</v>
@@ -2717,7 +2717,7 @@
         <v>0.8</v>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="R29" s="2" t="n">
         <v>0.833</v>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>5</v>

--- a/Task4_交付物/metadata_filter_test.xlsx
+++ b/Task4_交付物/metadata_filter_test.xlsx
@@ -618,10 +618,10 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>345</v>
+        <v>324</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>5</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>0.857</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -696,10 +696,10 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1521</v>
+        <v>1535</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>5</v>
@@ -715,16 +715,16 @@
         </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>0.833</v>
+        <v>1</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0.833</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -774,10 +774,10 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>924</v>
+        <v>899</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>452</v>
+        <v>427</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>5</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="5">
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>978</v>
+        <v>966</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>463</v>
+        <v>437</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>5</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>0.444</v>
+        <v>1</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.444</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>893</v>
+        <v>880</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>539</v>
+        <v>506</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>5</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -1008,10 +1008,10 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1294</v>
+        <v>1309</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>5</v>
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1067</v>
+        <v>1042</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>627</v>
+        <v>601</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>5</v>
@@ -1167,7 +1167,7 @@
         <v>800</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>351</v>
+        <v>331</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>5</v>
@@ -1242,10 +1242,10 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1335</v>
+        <v>1319</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1035</v>
+        <v>1015</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>5</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>505</v>
+        <v>479</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>5</v>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1491</v>
+        <v>1483</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1491</v>
+        <v>1483</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="O12" s="2" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q12" s="2" t="n">
         <v>1</v>
@@ -1468,10 +1468,10 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>285</v>
+        <v>260</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>285</v>
+        <v>260</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1612,10 +1612,10 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>5</v>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>5</v>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>976</v>
+        <v>943</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>532</v>
+        <v>499</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>5</v>
@@ -1787,16 +1787,16 @@
         </is>
       </c>
       <c r="O17" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="R17" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1101</v>
+        <v>1081</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>600</v>
+        <v>569</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>5</v>
@@ -1871,10 +1871,10 @@
         <v>1</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1433</v>
+        <v>1396</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>978</v>
+        <v>941</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>5</v>
@@ -1949,10 +1949,10 @@
         <v>1</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>0.444</v>
+        <v>0.8</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>0.444</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="20">
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>852</v>
+        <v>845</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>339</v>
+        <v>318</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>5</v>
@@ -2017,16 +2017,16 @@
         </is>
       </c>
       <c r="O20" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="P20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>0.222</v>
+        <v>1</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>0.222</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>475</v>
+        <v>444</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>5</v>
@@ -2104,7 +2104,7 @@
         <v>1</v>
       </c>
       <c r="R21" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -2154,10 +2154,10 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1528</v>
+        <v>1553</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1190</v>
+        <v>1193</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>5</v>
@@ -2232,10 +2232,10 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>726</v>
+        <v>692</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>403</v>
+        <v>369</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>5</v>
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="O23" s="2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="2" t="n">
         <v>0.75</v>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1324</v>
+        <v>1315</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>1043</v>
+        <v>1017</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>5</v>
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>914</v>
+        <v>900</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>633</v>
+        <v>602</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>5</v>
@@ -2407,16 +2407,16 @@
         </is>
       </c>
       <c r="O25" s="2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>0.75</v>
+        <v>0.833</v>
       </c>
       <c r="R25" s="2" t="n">
-        <v>0.75</v>
+        <v>0.833</v>
       </c>
     </row>
     <row r="26">
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>947</v>
+        <v>918</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>454</v>
+        <v>418</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>5</v>
@@ -2614,7 +2614,7 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1535</v>
+        <v>1552</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>1252</v>
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>490</v>
+        <v>457</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>5</v>
@@ -2717,10 +2717,10 @@
         <v>0.8</v>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>0.833</v>
+        <v>1</v>
       </c>
       <c r="R29" s="2" t="n">
-        <v>0.833</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1185</v>
+        <v>1203</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1185</v>
+        <v>1203</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1381</v>
+        <v>1364</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1079</v>
+        <v>1058</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>5</v>
@@ -2862,13 +2862,13 @@
         <v>1</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Q31" s="2" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="R31" s="2" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
     </row>
   </sheetData>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>

--- a/Task4_交付物/metadata_filter_test.xlsx
+++ b/Task4_交付物/metadata_filter_test.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Filter Test'!$A$1:$R$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Drop Log'!$A$1:$E$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Drop Log'!$A$1:$E$151</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -618,17 +618,17 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>853</v>
+        <v>863</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>324</v>
+        <v>672</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -696,17 +696,17 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1535</v>
+        <v>1162</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1144</v>
+        <v>971</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -774,17 +774,17 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>899</v>
+        <v>859</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>427</v>
+        <v>696</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -852,17 +852,17 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>966</v>
+        <v>927</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>437</v>
+        <v>736</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -930,17 +930,17 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>880</v>
+        <v>916</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>506</v>
+        <v>719</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,17 +1008,17 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1309</v>
+        <v>1353</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>864</v>
+        <v>1119</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1086,17 +1086,17 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1042</v>
+        <v>1204</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>601</v>
+        <v>957</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1167,14 +1167,14 @@
         <v>800</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>331</v>
+        <v>600</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1242,17 +1242,17 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1319</v>
+        <v>1059</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1015</v>
+        <v>875</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1320,17 +1320,17 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>853</v>
+        <v>912</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>479</v>
+        <v>715</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
         <v>1</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Q11" s="2" t="n">
         <v>0.6</v>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1483</v>
+        <v>1455</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1483</v>
+        <v>1455</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1468,10 +1468,10 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>260</v>
+        <v>142</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>260</v>
+        <v>142</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1538,10 +1538,10 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>800</v>
+        <v>581</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>800</v>
+        <v>581</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1612,17 +1612,17 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1008</v>
+        <v>962</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>625</v>
+        <v>783</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1690,17 +1690,17 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1031</v>
+        <v>997</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1768,17 +1768,17 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>943</v>
+        <v>1070</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>499</v>
+        <v>855</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1846,17 +1846,17 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1081</v>
+        <v>1253</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>569</v>
+        <v>942</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1924,17 +1924,17 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1396</v>
+        <v>1092</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>941</v>
+        <v>871</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1998,17 +1998,17 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>845</v>
+        <v>857</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>318</v>
+        <v>667</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2076,17 +2076,17 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>846</v>
+        <v>906</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>444</v>
+        <v>716</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2154,17 +2154,17 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1553</v>
+        <v>1234</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1193</v>
+        <v>1051</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2232,17 +2232,17 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>692</v>
+        <v>939</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>369</v>
+        <v>759</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="O23" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="Q23" s="2" t="n">
         <v>0.75</v>
@@ -2310,17 +2310,17 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1315</v>
+        <v>1038</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>1017</v>
+        <v>850</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2388,17 +2388,17 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>900</v>
+        <v>936</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>602</v>
+        <v>748</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>800</v>
+        <v>660</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>800</v>
+        <v>660</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="O26" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Q26" s="2" t="n">
         <v>1</v>
@@ -2536,17 +2536,17 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>918</v>
+        <v>1079</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>418</v>
+        <v>810</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2614,17 +2614,17 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1552</v>
+        <v>1198</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1252</v>
+        <v>1008</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2692,17 +2692,17 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>859</v>
+        <v>898</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>457</v>
+        <v>709</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2711,10 +2711,10 @@
         </is>
       </c>
       <c r="O29" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="Q29" s="2" t="n">
         <v>1</v>
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1203</v>
+        <v>1048</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1203</v>
+        <v>1048</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="O30" s="2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="Q30" s="2" t="n">
         <v>0.6</v>
@@ -2840,17 +2840,17 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1364</v>
+        <v>1110</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1058</v>
+        <v>923</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="O31" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="P31" s="2" t="n">
         <v>0.8</v>
@@ -2883,7 +2883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E126"/>
+  <dimension ref="A1:E151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3058,12 +3058,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Q002</t>
+          <t>Q001</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Q003</t>
+          <t>Q002</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Q003</t>
+          <t>Q002</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -3316,24 +3316,24 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Q004</t>
+          <t>Q003</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -3343,24 +3343,24 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Q004</t>
+          <t>Q003</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -3370,24 +3370,24 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Q004</t>
+          <t>Q003</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -3424,12 +3424,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -3451,24 +3451,24 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Q005</t>
+          <t>Q004</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Q005</t>
+          <t>Q004</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -3505,24 +3505,24 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Q005</t>
+          <t>Q004</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -3532,24 +3532,24 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Q005</t>
+          <t>Q004</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -3586,24 +3586,24 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q005</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q005</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q005</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -3667,24 +3667,24 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q005</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -3694,19 +3694,19 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q005</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -3733,12 +3733,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3748,24 +3748,24 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3787,12 +3787,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3802,24 +3802,24 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3841,12 +3841,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3883,24 +3883,24 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3910,24 +3910,24 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3937,24 +3937,24 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3991,24 +3991,24 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -4030,12 +4030,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -4045,24 +4045,24 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -4072,24 +4072,24 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -4099,24 +4099,24 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4126,24 +4126,24 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Q010</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Q010</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Q010</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4207,24 +4207,24 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Q010</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4234,24 +4234,24 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Q010</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4261,24 +4261,24 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4288,24 +4288,24 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4342,24 +4342,24 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4369,24 +4369,24 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4396,19 +4396,19 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4462,7 +4462,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -4489,12 +4489,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4516,7 +4516,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4624,7 +4624,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4666,24 +4666,24 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -4693,19 +4693,19 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -4786,12 +4786,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Q018</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Q018</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4855,19 +4855,19 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Q018</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Q018</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4909,24 +4909,24 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Q018</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4936,24 +4936,24 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Q019</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4963,24 +4963,24 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Q019</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Q019</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -5017,24 +5017,24 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Q019</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -5044,24 +5044,24 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Q019</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5071,24 +5071,24 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -5125,24 +5125,24 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -5152,24 +5152,24 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -5179,24 +5179,24 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q018</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5206,24 +5206,24 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q018</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q018</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5272,7 +5272,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q018</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q018</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5326,7 +5326,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q018</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -5380,7 +5380,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -5407,12 +5407,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5434,12 +5434,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5449,19 +5449,19 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -5488,12 +5488,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -5503,24 +5503,24 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -5569,12 +5569,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -5584,24 +5584,24 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -5611,24 +5611,24 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -5638,24 +5638,24 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -5665,24 +5665,24 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -5719,24 +5719,24 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Q026</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Q026</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -5812,12 +5812,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Q026</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -5827,24 +5827,24 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Q026</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -5854,24 +5854,24 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Q026</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -5881,24 +5881,24 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -5935,24 +5935,24 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -5962,24 +5962,24 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -5989,24 +5989,24 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -6016,19 +6016,19 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -6055,7 +6055,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -6082,7 +6082,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -6109,7 +6109,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -6136,7 +6136,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -6190,12 +6190,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -6217,12 +6217,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -6232,19 +6232,19 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6271,32 +6271,707 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>Q024</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Q024</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>MCK_001</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Q026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Q026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>IMF_001</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Q026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Q026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Q026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Q026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>MCK_001</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Q027</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Q027</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Q027</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Q027</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>IMF_001</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Q027</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Q027</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>MCK_001</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Q028</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Q028</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Q028</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>IMF_001</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Q028</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Q028</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Q028</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>MCK_001</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
           <t>Q030</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Q030</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Q030</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Q030</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Q030</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>IMF_001</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Q030</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>MCK_001</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>F1:macro-drift</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>宏观风险</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E126"/>
+  <autoFilter ref="A1:E151"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Task4_交付物/metadata_filter_test.xlsx
+++ b/Task4_交付物/metadata_filter_test.xlsx
@@ -14,8 +14,8 @@
     <sheet name="Schema Derivation" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Filter Test'!$A$1:$R$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Drop Log'!$A$1:$E$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Filter Test'!$A$1:$R$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Drop Log'!$A$1:$E$190</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R31"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -618,17 +618,17 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>863</v>
+        <v>878</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>672</v>
+        <v>748</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -696,17 +696,17 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1162</v>
+        <v>1224</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>971</v>
+        <v>1114</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -774,17 +774,17 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>859</v>
+        <v>965</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>696</v>
+        <v>839</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
         <v>0.333</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="5">
@@ -852,17 +852,17 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>927</v>
+        <v>950</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>736</v>
+        <v>820</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -930,10 +930,10 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>916</v>
+        <v>922</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>719</v>
+        <v>797</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>6</v>
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="O6" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Q6" s="2" t="n">
         <v>1</v>
@@ -1004,21 +1004,21 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>出口管制/出口管制/关税/原产地与转运/反规避/贸易流</t>
+          <t>出口管制/出口管制/关税/原产地与转运/反规避/市场准入/本地化政策/贸易流</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1353</v>
+        <v>1446</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1119</v>
+        <v>1281</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1204</v>
+        <v>1335</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>957</v>
+        <v>1218</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>6</v>
@@ -1105,10 +1105,10 @@
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Q8" s="2" t="n">
         <v>1</v>
@@ -1167,7 +1167,7 @@
         <v>800</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>600</v>
+        <v>667</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>6</v>
@@ -1238,21 +1238,21 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>供应链布局/出口管制/出口管制/关税/原产地与转运/反规避/贸易流</t>
+          <t>供应链布局/出口管制/出口管制/关税/原产地与转运/反规避/市场准入/本地化政策/贸易流</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1059</v>
+        <v>1076</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>875</v>
+        <v>1002</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>912</v>
+        <v>938</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>715</v>
+        <v>813</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>6</v>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="P11" s="2" t="n">
         <v>0.8</v>
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1455</v>
+        <v>1481</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1455</v>
+        <v>1481</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="O12" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q12" s="2" t="n">
         <v>1</v>
@@ -1468,10 +1468,10 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1538,10 +1538,10 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>581</v>
+        <v>800</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>581</v>
+        <v>800</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1608,21 +1608,21 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>出口管制/出口管制/关税/原产地与转运/反规避/贸易流</t>
+          <t>出口管制/出口管制/关税/原产地与转运/反规避/市场准入/本地化政策/贸易流</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>962</v>
+        <v>1013</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>783</v>
+        <v>913</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1686,21 +1686,21 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>关税/出口管制/出口管制/关税/原产地与转运/反规避/贸易流</t>
+          <t>关税/出口管制/出口管制/关税/原产地与转运/反规避/市场准入/本地化政策/贸易流</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>997</v>
+        <v>1023</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>866</v>
+        <v>976</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1070</v>
+        <v>1244</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>855</v>
+        <v>1084</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>6</v>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="O17" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q17" s="2" t="n">
         <v>1</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1253</v>
+        <v>1479</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>942</v>
+        <v>1284</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>6</v>
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1092</v>
+        <v>1118</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>871</v>
+        <v>950</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>6</v>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="O19" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="Q19" s="2" t="n">
         <v>0.8</v>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>857</v>
+        <v>1107</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>667</v>
+        <v>978</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>6</v>
@@ -2023,10 +2023,10 @@
         <v>1</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
     </row>
     <row r="21">
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>906</v>
+        <v>924</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>716</v>
+        <v>776</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>6</v>
@@ -2150,21 +2150,21 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>供应链布局/出口管制/出口管制/关税/原产地与转运/反规避/贸易流</t>
+          <t>供应链布局/出口管制/出口管制/关税/原产地与转运/反规避/市场准入/本地化政策/贸易流</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1234</v>
+        <v>1434</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1051</v>
+        <v>1332</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2228,21 +2228,21 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>出口管制/出口管制/关税/原产地与转运/反规避/贸易流</t>
+          <t>出口管制/出口管制/关税/原产地与转运/反规避/市场准入/本地化政策/贸易流</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>939</v>
+        <v>1080</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>759</v>
+        <v>982</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2306,14 +2306,14 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>供应链布局/出口管制/出口管制/关税/原产地与转运/反规避/贸易流</t>
+          <t>供应链布局/出口管制/出口管制/关税/原产地与转运/反规避/市场准入/本地化政策/贸易流</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1038</v>
+        <v>1046</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>850</v>
+        <v>942</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>6</v>
@@ -2384,14 +2384,14 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>供应链布局/出口管制/出口管制/关税/原产地与转运/反规避/贸易流</t>
+          <t>供应链布局/出口管制/出口管制/关税/原产地与转运/反规避/市场准入/本地化政策/贸易流</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>936</v>
+        <v>1186</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>748</v>
+        <v>1081</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>6</v>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>660</v>
+        <v>800</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>660</v>
+        <v>800</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="O26" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="Q26" s="2" t="n">
         <v>1</v>
@@ -2532,14 +2532,14 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>出口管制/出口管制/关税/原产地与转运/反规避/贸易流</t>
+          <t>出口管制/出口管制/关税/原产地与转运/反规避/市场准入/本地化政策/贸易流</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1079</v>
+        <v>1413</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>810</v>
+        <v>1201</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>6</v>
@@ -2610,14 +2610,14 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>供应链布局/出口管制/出口管制/关税/原产地与转运/反规避/贸易流</t>
+          <t>供应链布局/出口管制/出口管制/关税/原产地与转运/反规避/市场准入/本地化政策/贸易流</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1198</v>
+        <v>1401</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1008</v>
+        <v>1295</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>6</v>
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>898</v>
+        <v>927</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>709</v>
+        <v>780</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>6</v>
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1048</v>
+        <v>1076</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1048</v>
+        <v>1076</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="O30" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q30" s="2" t="n">
         <v>0.6</v>
@@ -2836,21 +2836,21 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>供应链布局/出口管制/出口管制/关税/原产地与转运/反规避/贸易流</t>
+          <t>供应链布局/出口管制/出口管制/关税/原产地与转运/反规避/市场准入/本地化政策/贸易流</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1110</v>
+        <v>1121</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>923</v>
+        <v>1044</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2871,8 +2871,760 @@
         <v>0.571</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>我们在评估把电池与整车产能分散到中国以外，是否真能降低关税与物流成本。特斯拉最新年报对其全球制造布局与关税影响的原始披露说明了什么？</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>tariff/supply_chain/logistics</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk/Supply Chain Risk/Operational Risk</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>供应链布局/关税/出口管制/关税/原产地与转运/物流/贸易流</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>947</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>796</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>export_control</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>如果管理层要评估美国对华出口管制与关税升级对整车企业采购端的直接影响，蔚来、小鹏、理想三家在美股年报中分别披露了哪些制造基地，以及哪些与出口管制/关税相关的供应链风险？</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>export_control/tariff/market_access/supply_chain</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk/Supply Chain Risk/Regulatory Risk/Market Access Risk/Operational Risk</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>供应链布局/关税/出口管制/出口管制/关税/原产地与转运/反规避/市场准入/本地化政策/贸易流</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>1320</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>1218</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001; EU_004; IMF_001; UNCTAD_001; WEF_001</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>0.667</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>我们要评估锂盐供应在贸易政策变化下的脆弱性。雅保（Albemarle）最新年报如何披露其锂资源与转化加工的全球布局，以及相关的贸易政策风险？</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy/supply_chain</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk/Market Access Risk/Supply Chain Risk/Operational Risk</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>供应链布局/出口管制/关税/原产地与转运/反规避/贸易流</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>786</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001; EU_004; IMF_001; UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>假设我们把电池包组装放在墨西哥、电芯仍从中国采购，要享受USMCA优惠关税必须满足什么原产地成分门槛？</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>CN/MX</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>tariff/trade_policy</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk/Market Access Risk</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>供应链布局/关税/出口管制/关税/原产地与转运/反规避/贸易流</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>991</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>920</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001; EU_004; IMF_001; UNCTAD_001; WEF_001</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>我们准备在印度本地建厂以服务当地市场，印度当前的进口关税水平与贸易/本地化政策基线是什么？</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>tariff/supply_chain/localization_policy</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk/Supply Chain Risk/Operational Risk/Regulatory Risk/Market Access Risk</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>供应链布局/关税/出口管制/关税/原产地与转运/市场准入/本地化政策/贸易流</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>1171</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>1074</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001; EU_004; IMF_001; UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>localization_policy</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>印尼对镍与电池产业链设置了哪些本地含量和矿产下游化要求，会影响我们在当地的投资与采购安排？</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>246</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001; UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>如果产能从中国转移到越南、印尼或墨西哥，物流与通关效率会带来多大额外成本？有没有可量化的基准？</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>CN/VN/ID/MX</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain/logistics</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk/Operational Risk</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>供应链布局/原产地与转运/物流/贸易流</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>1162</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>995</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>labor</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>电池材料出口到美国时，哪些强迫劳动合规要求会直接限制我们的供应商选择？</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory Risk/Market Access Risk/Trade Risk</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>出口管制/原产地与转运/反规避/市场准入/本地化政策/贸易流</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>1544</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>1388</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>全球动力电池供给的集中度到底有多高？有没有最新数据说明中国供应商的份额？</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="n">
+        <v>1114</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>895</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Scenario Simulation Support</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>董事会要在「保留中国产能」「迁往墨西哥」「迁往印尼」之间取舍，现有证据分别能支撑哪些关键判断（原产地门槛、本地含量要求、物流成本）？</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>CN/ID/MX</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy/supply_chain/logistics</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk/Trade Risk/Market Access Risk/Operational Risk</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>供应链布局/出口管制/关税/原产地与转运/反规避/物流/贸易流</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>1045</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>899</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R31"/>
+  <autoFilter ref="A1:R41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2883,7 +3635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E151"/>
+  <dimension ref="A1:E190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3058,12 +3810,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Q001</t>
+          <t>Q002</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -3090,7 +3842,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -3117,7 +3869,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -3144,7 +3896,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -3154,12 +3906,12 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3923,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -3181,24 +3933,24 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Q002</t>
+          <t>Q003</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -3220,12 +3972,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Q002</t>
+          <t>Q003</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -3235,12 +3987,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
@@ -3252,7 +4004,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -3279,7 +4031,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -3289,12 +4041,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
@@ -3306,7 +4058,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -3316,24 +4068,24 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Q003</t>
+          <t>Q004</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -3343,24 +4095,24 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Q003</t>
+          <t>Q004</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -3370,24 +4122,24 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Q003</t>
+          <t>Q004</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -3414,7 +4166,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -3424,12 +4176,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
@@ -3441,7 +4193,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -3451,24 +4203,24 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Q004</t>
+          <t>Q005</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -3490,12 +4242,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Q004</t>
+          <t>Q005</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -3505,24 +4257,24 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Q004</t>
+          <t>Q005</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -3532,24 +4284,24 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Q004</t>
+          <t>Q005</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -3559,12 +4311,12 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
@@ -3576,7 +4328,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -3603,7 +4355,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -3613,24 +4365,24 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Q005</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -3652,12 +4404,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Q005</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -3667,24 +4419,24 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Q005</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -3694,24 +4446,24 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Q005</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -3721,12 +4473,12 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
@@ -3738,7 +4490,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3760,12 +4512,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3775,24 +4527,24 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3802,24 +4554,24 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3841,12 +4593,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3868,12 +4620,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3883,12 +4635,12 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
@@ -3900,7 +4652,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3922,12 +4674,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3949,12 +4701,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3964,24 +4716,24 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -4003,7 +4755,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -4030,12 +4782,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -4045,12 +4797,12 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4814,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -4072,24 +4824,24 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -4099,19 +4851,19 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -4138,12 +4890,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4153,19 +4905,19 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -4192,12 +4944,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4207,19 +4959,19 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -4246,7 +4998,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -4273,12 +5025,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4288,24 +5040,24 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4315,19 +5067,19 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -4354,7 +5106,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -4381,12 +5133,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Q010</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4408,12 +5160,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Q010</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4435,12 +5187,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Q010</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4462,7 +5214,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Q010</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -4489,12 +5241,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Q010</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4516,12 +5268,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Q010</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4531,24 +5283,24 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4570,12 +5322,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -4585,24 +5337,24 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -4624,12 +5376,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -4639,24 +5391,24 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4678,12 +5430,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -4693,24 +5445,24 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -4732,12 +5484,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -4747,24 +5499,24 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4774,24 +5526,24 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4801,24 +5553,24 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4840,12 +5592,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4855,19 +5607,19 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4894,12 +5646,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4909,24 +5661,24 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4948,12 +5700,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4975,12 +5727,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q018</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -5002,12 +5754,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q018</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -5017,24 +5769,24 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>Q018</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -5056,12 +5808,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>Q018</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -5071,24 +5823,24 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>Q018</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5110,12 +5862,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>Q018</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -5137,12 +5889,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -5152,24 +5904,24 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -5191,12 +5943,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Q018</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -5218,12 +5970,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Q018</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5245,12 +5997,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Q018</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5260,19 +6012,19 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Q018</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -5299,12 +6051,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Q018</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5326,12 +6078,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Q018</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -5341,24 +6093,24 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Q019</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -5380,12 +6132,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Q019</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5407,12 +6159,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Q019</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -5422,24 +6174,24 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Q019</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -5449,24 +6201,24 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Q019</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5476,24 +6228,24 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Q019</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -5503,24 +6255,24 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -5530,24 +6282,24 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -5569,7 +6321,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -5596,12 +6348,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -5623,12 +6375,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -5638,24 +6390,24 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -5665,24 +6417,24 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -5692,24 +6444,24 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -5719,24 +6471,24 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -5746,24 +6498,24 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -5785,12 +6537,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -5812,12 +6564,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -5827,24 +6579,24 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -5854,24 +6606,24 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -5881,24 +6633,24 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -5920,12 +6672,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -5935,24 +6687,24 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -5962,24 +6714,24 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -6001,12 +6753,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -6016,24 +6768,24 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -6043,24 +6795,24 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -6082,7 +6834,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -6109,12 +6861,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -6124,24 +6876,24 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -6163,7 +6915,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -6190,12 +6942,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -6205,24 +6957,24 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q027</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -6244,12 +6996,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q027</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -6271,12 +7023,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q027</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -6286,24 +7038,24 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q027</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -6313,24 +7065,24 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Q026</t>
+          <t>Q027</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -6340,24 +7092,24 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Q026</t>
+          <t>Q027</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -6367,24 +7119,24 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Q026</t>
+          <t>Q028</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -6406,12 +7158,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Q026</t>
+          <t>Q028</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -6421,24 +7173,24 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Q026</t>
+          <t>Q028</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -6460,12 +7212,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Q026</t>
+          <t>Q028</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -6487,12 +7239,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q028</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -6514,12 +7266,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q028</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -6529,24 +7281,24 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -6568,12 +7320,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -6595,12 +7347,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -6610,24 +7362,24 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -6649,12 +7401,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q030</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -6676,12 +7428,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q031</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -6703,12 +7455,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q031</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -6730,7 +7482,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q031</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -6757,12 +7509,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q031</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -6784,12 +7536,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q031</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -6799,24 +7551,24 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q031</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -6826,24 +7578,24 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q032</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -6865,12 +7617,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q032</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -6892,12 +7644,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q032</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -6907,24 +7659,24 @@
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q032</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -6934,44 +7686,1097 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q032</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>IMF_001</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>IMF_001</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>IMF_001</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>IMF_001</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
           <t>MCK_001</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>F1:macro-drift</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>宏观风险</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>IMF_001</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>MCK_001</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>IMF_001</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>MCK_001</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>IMF_001</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>MCK_001</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E151"/>
+  <autoFilter ref="A1:E190"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7093,7 +8898,7 @@
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>供应链布局/出口管制/原产地与转运/反规避/贸易流</t>
+          <t>供应链布局/出口管制/原产地与转运/反规避/市场准入/本地化政策/贸易流</t>
         </is>
       </c>
     </row>
@@ -7126,7 +8931,7 @@
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>出口管制/原产地与转运/反规避/贸易流</t>
+          <t>出口管制/原产地与转运/反规避/市场准入/本地化政策/贸易流</t>
         </is>
       </c>
     </row>
@@ -7291,7 +9096,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>供应链布局/出口管制/出口管制/关税/原产地与转运/反规避/贸易流</t>
+          <t>供应链布局/出口管制/出口管制/关税/原产地与转运/反规避/市场准入/本地化政策/贸易流</t>
         </is>
       </c>
     </row>
@@ -7821,7 +9626,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>直接沿用（S / A+ / A / B+）</t>
+          <t>直接沿用（S / A+ / A / B+ / B）</t>
         </is>
       </c>
     </row>

--- a/Task4_交付物/metadata_filter_test.xlsx
+++ b/Task4_交付物/metadata_filter_test.xlsx
@@ -14,8 +14,8 @@
     <sheet name="Schema Derivation" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Filter Test'!$A$1:$R$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Drop Log'!$A$1:$E$190</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Filter Test'!$A$1:$R$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Drop Log'!$A$1:$E$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R41"/>
+  <dimension ref="A1:R44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2232,10 +2232,10 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>5</v>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>5</v>
@@ -3292,10 +3292,10 @@
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>2</v>
@@ -3470,7 +3470,7 @@
         <v>0.6</v>
       </c>
       <c r="P39" s="2" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="Q39" s="2" t="n">
         <v>1</v>
@@ -3514,10 +3514,10 @@
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="n">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>6</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="O40" s="2" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="P40" s="2" t="n">
         <v>0.4</v>
@@ -3623,8 +3623,238 @@
         <v>1</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>我们准备向欧盟出口 EV 电池。欧盟电池法规对进入欧盟市场的电池提出了哪些强制合规要求（碳足迹、再生材料含量、供应链尽职调查、电池护照）？</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>market_access/supply_chain/regulation</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk/Regulatory Risk/Market Access Risk/Trade Risk/Operational Risk</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>供应链布局/出口管制/出口管制/关税/原产地与转运/反规避/市场准入/本地化政策/贸易流</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>1523</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>1302</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>欧盟对中国产纯电动车征收的最终反补贴税税率是多少？不同企业（比亚迪/吉利/上汽/特斯拉）的税率差异如何？</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>CN/EU</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk/Market Access Risk</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>供应链布局/出口管制/关税/原产地与转运/反规避/贸易流</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>1400</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>1210</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001; EU_004; IMF_001; UNCTAD_001; WEF_001</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R43" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>如果中国电池企业要在欧盟建厂或收购当地电池资产，欧盟层面的外资安全审查框架和关键原材料法案会带来哪些约束（审查范围、本土化与单一第三国依赖目标）？</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>EV_Battery</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>CN/EU</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy/supply_chain</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk/Regulatory Risk/Supply Chain Risk/Operational Risk</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>供应链布局/原产地与转运/宏观风险/对外投资/贸易流</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>1346</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>1346</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R41"/>
+  <autoFilter ref="A1:R44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3635,7 +3865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E190"/>
+  <dimension ref="A1:E201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8775,8 +9005,305 @@
         </is>
       </c>
     </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>IMF_001</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>MCK_001</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>IMF_001</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E190"/>
+  <autoFilter ref="A1:E201"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Task4_交付物/metadata_filter_test.xlsx
+++ b/Task4_交付物/metadata_filter_test.xlsx
@@ -618,10 +618,10 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>5</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>5</v>
@@ -1008,10 +1008,10 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>5</v>
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="O19" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P19" s="2" t="n">
         <v>0.8</v>
-      </c>
-      <c r="P19" s="2" t="n">
-        <v>0.6</v>
       </c>
       <c r="Q19" s="2" t="n">
         <v>0.8</v>
@@ -1998,10 +1998,10 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>6</v>
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2996,10 +2996,10 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>5</v>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1171</v>
+        <v>1175</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>4</v>

--- a/Task4_交付物/metadata_filter_test.xlsx
+++ b/Task4_交付物/metadata_filter_test.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Filter Test'!$A$1:$R$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Drop Log'!$A$1:$E$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Drop Log'!$A$1:$E$347</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -618,17 +618,17 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>881</v>
+        <v>1084</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; IMF_001; MCK_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -696,17 +696,17 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1224</v>
+        <v>1536</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1114</v>
+        <v>1106</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="P3" s="2" t="n">
         <v>0.6</v>
@@ -774,17 +774,17 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>965</v>
+        <v>1269</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>839</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; IMF_001; MCK_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -852,17 +852,17 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>953</v>
+        <v>1251</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>823</v>
+        <v>828</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; IMF_001; MCK_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -930,17 +930,17 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>922</v>
+        <v>1096</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>797</v>
+        <v>786</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,17 +1008,17 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1447</v>
+        <v>1459</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1282</v>
+        <v>1012</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1086,17 +1086,17 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1335</v>
+        <v>1370</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1218</v>
+        <v>1089</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1167,14 +1167,14 @@
         <v>800</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>667</v>
+        <v>562</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1242,17 +1242,17 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1076</v>
+        <v>1388</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1002</v>
+        <v>994</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1320,17 +1320,17 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>938</v>
+        <v>1050</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>813</v>
+        <v>802</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1398,10 +1398,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1481</v>
+        <v>1527</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1481</v>
+        <v>1527</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1413,10 +1413,10 @@
         </is>
       </c>
       <c r="O12" s="2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="Q12" s="2" t="n">
         <v>1</v>
@@ -1468,10 +1468,10 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>159</v>
+        <v>479</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>159</v>
+        <v>479</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="O13" s="2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="Q13" s="2" t="n">
         <v>0.5</v>
@@ -1612,17 +1612,17 @@
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1013</v>
+        <v>1136</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>913</v>
+        <v>905</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1690,17 +1690,17 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1023</v>
+        <v>1128</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>976</v>
+        <v>967</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1768,17 +1768,17 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1244</v>
+        <v>1388</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
         <v>0.6</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="R17" s="2" t="n">
         <v>1</v>
@@ -1846,17 +1846,17 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1479</v>
+        <v>1483</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1284</v>
+        <v>1171</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1924,17 +1924,17 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1118</v>
+        <v>1437</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
         <v>0.6</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q19" s="2" t="n">
         <v>0.8</v>
@@ -1998,17 +1998,17 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1110</v>
+        <v>1209</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2017,13 +2017,13 @@
         </is>
       </c>
       <c r="O20" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="P20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>0.833</v>
+        <v>0.667</v>
       </c>
       <c r="R20" s="2" t="n">
         <v>0.833</v>
@@ -2076,17 +2076,17 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>924</v>
+        <v>1200</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2154,17 +2154,17 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1434</v>
+        <v>1528</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1332</v>
+        <v>1212</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2232,17 +2232,17 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1081</v>
+        <v>1334</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>983</v>
+        <v>934</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; IMF_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2310,17 +2310,17 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1046</v>
+        <v>1257</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>942</v>
+        <v>927</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2388,17 +2388,17 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1186</v>
+        <v>1274</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>1081</v>
+        <v>1067</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2477,16 +2477,16 @@
         </is>
       </c>
       <c r="O26" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="27">
@@ -2536,17 +2536,17 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1413</v>
+        <v>1449</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1201</v>
+        <v>967</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="O27" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="P27" s="2" t="n">
         <v>0.8</v>
@@ -2614,17 +2614,17 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1401</v>
+        <v>1532</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1295</v>
+        <v>1103</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2692,17 +2692,17 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>927</v>
+        <v>1046</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>780</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2711,10 +2711,10 @@
         </is>
       </c>
       <c r="O29" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Q29" s="2" t="n">
         <v>1</v>
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1079</v>
+        <v>1403</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1079</v>
+        <v>1403</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2840,17 +2840,17 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1121</v>
+        <v>1330</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1044</v>
+        <v>1036</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -2918,17 +2918,17 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>947</v>
+        <v>1029</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="L32" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2996,17 +2996,17 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1323</v>
+        <v>1569</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>1221</v>
+        <v>1198</v>
       </c>
       <c r="L33" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -3073,14 +3073,14 @@
         <v>800</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>786</v>
+        <v>604</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; UNCTAD_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="O34" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="P34" s="2" t="n">
         <v>0.8</v>
@@ -3148,17 +3148,17 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>992</v>
+        <v>1017</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>921</v>
+        <v>911</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -3226,17 +3226,17 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1175</v>
+        <v>1354</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>1078</v>
+        <v>1084</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; UNCTAD_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3292,17 +3292,17 @@
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="n">
-        <v>255</v>
+        <v>396</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>247</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; UNCTAD_001</t>
+          <t>CNGOV_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -3311,7 +3311,7 @@
         </is>
       </c>
       <c r="O37" s="2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="P37" s="2" t="n">
         <v>0.8</v>
@@ -3370,17 +3370,17 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1162</v>
+        <v>1425</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -3448,17 +3448,17 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>1388</v>
+        <v>1230</v>
       </c>
       <c r="L39" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="O39" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P39" s="2" t="n">
         <v>0.6</v>
-      </c>
-      <c r="P39" s="2" t="n">
-        <v>0.4</v>
       </c>
       <c r="Q39" s="2" t="n">
         <v>1</v>
@@ -3514,17 +3514,17 @@
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="n">
-        <v>1115</v>
+        <v>1248</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>896</v>
       </c>
       <c r="L40" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3592,17 +3592,17 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1045</v>
+        <v>1284</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="L41" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -3670,17 +3670,17 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1523</v>
+        <v>1518</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>1302</v>
+        <v>1181</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; MCK_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MCK_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -3692,7 +3692,7 @@
         <v>0.4</v>
       </c>
       <c r="P42" s="2" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q42" s="2" t="n">
         <v>1</v>
@@ -3748,17 +3748,17 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1400</v>
+        <v>1545</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1210</v>
+        <v>1153</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001; EU_004; IMF_001; UNCTAD_001; WEF_001</t>
+          <t>CNGOV_001; EU_004; IMF_001; MOFCOM_003; MOFCOM_004; MOFCOM_005; MOFCOM_006; UNCTAD_001; WEF_001</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1346</v>
+        <v>1512</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>1346</v>
+        <v>1512</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -3865,7 +3865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E201"/>
+  <dimension ref="A1:E347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MOFCOM_006</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MOFCOM_005</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -4028,24 +4028,24 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Q002</t>
+          <t>Q001</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Q002</t>
+          <t>Q001</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -4094,12 +4094,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Q002</t>
+          <t>Q001</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -4109,19 +4109,19 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Q002</t>
+          <t>Q001</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Q003</t>
+          <t>Q002</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Q003</t>
+          <t>Q002</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MOFCOM_006</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Q003</t>
+          <t>Q002</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>MOFCOM_005</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -4256,12 +4256,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Q003</t>
+          <t>Q002</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -4271,24 +4271,24 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Q003</t>
+          <t>Q002</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -4298,24 +4298,24 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Q004</t>
+          <t>Q002</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -4337,12 +4337,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Q004</t>
+          <t>Q002</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -4352,24 +4352,24 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Q004</t>
+          <t>Q002</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -4391,12 +4391,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Q004</t>
+          <t>Q003</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -4406,24 +4406,24 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Q004</t>
+          <t>Q003</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MOFCOM_005</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -4433,24 +4433,24 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Q005</t>
+          <t>Q003</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>MOFCOM_006</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -4472,12 +4472,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Q005</t>
+          <t>Q003</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -4499,12 +4499,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Q005</t>
+          <t>Q003</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Q005</t>
+          <t>Q003</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -4541,24 +4541,24 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Q005</t>
+          <t>Q003</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Q005</t>
+          <t>Q003</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q003</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -4622,24 +4622,24 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q004</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q004</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MOFCOM_005</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -4676,24 +4676,24 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q004</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>MOFCOM_006</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -4715,12 +4715,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Q006</t>
+          <t>Q004</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>Q004</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -4757,24 +4757,24 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>Q004</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>Q004</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>Q004</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -4838,24 +4838,24 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>Q004</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -4865,24 +4865,24 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Q007</t>
+          <t>Q005</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>MOFCOM_006</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -4892,24 +4892,24 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q005</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -4931,12 +4931,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q005</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MOFCOM_005</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -4946,24 +4946,24 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q005</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q005</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -5012,12 +5012,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q005</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q005</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -5054,24 +5054,24 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q005</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q005</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q005</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -5147,12 +5147,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>MOFCOM_005</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -5174,12 +5174,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Q009</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Q010</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>MOFCOM_006</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -5228,12 +5228,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Q010</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Q010</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Q010</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -5297,24 +5297,24 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Q010</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -5324,24 +5324,24 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Q010</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -5351,19 +5351,19 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q006</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -5390,12 +5390,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>MOFCOM_006</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -5417,12 +5417,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MOFCOM_005</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -5459,24 +5459,24 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Q014</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5513,24 +5513,24 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5567,24 +5567,24 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5606,12 +5606,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q007</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5660,12 +5660,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5702,24 +5702,24 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5729,24 +5729,24 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>MOFCOM_005</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Q016</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>MOFCOM_006</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5783,24 +5783,24 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5849,7 +5849,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -5876,12 +5876,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>MOFCOM_006</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Q017</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -5945,24 +5945,24 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Q018</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>MOFCOM_005</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -5984,12 +5984,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Q018</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6011,12 +6011,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Q018</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Q018</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6053,24 +6053,24 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Q018</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6080,24 +6080,24 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Q018</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6107,24 +6107,24 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Q019</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Q019</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MOFCOM_005</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6173,12 +6173,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Q019</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Q019</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Q019</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>MOFCOM_006</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6242,24 +6242,24 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Q019</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -6269,24 +6269,24 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -6308,12 +6308,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -6350,24 +6350,24 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -6389,12 +6389,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q010</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Q020</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>MOFCOM_006</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -6431,24 +6431,24 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>MOFCOM_005</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -6512,24 +6512,24 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -6551,12 +6551,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Q021</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -6578,12 +6578,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -6620,19 +6620,19 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q014</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MOFCOM_006</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -6674,24 +6674,24 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Q022</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -6701,24 +6701,24 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>MOFCOM_005</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -6767,7 +6767,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -6821,7 +6821,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -6863,24 +6863,24 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MOFCOM_005</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>MOFCOM_006</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -6998,24 +6998,24 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -7025,24 +7025,24 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Q026</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -7064,7 +7064,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Q026</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -7091,12 +7091,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Q026</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -7106,24 +7106,24 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Q026</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -7133,24 +7133,24 @@
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Q026</t>
+          <t>Q016</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -7160,24 +7160,24 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Q026</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>MOFCOM_005</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -7187,24 +7187,24 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -7226,12 +7226,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>MOFCOM_006</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -7280,12 +7280,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -7322,24 +7322,24 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Q027</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -7349,24 +7349,24 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -7376,24 +7376,24 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q017</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -7430,24 +7430,24 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q018</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MOFCOM_006</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -7457,24 +7457,24 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q018</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>MOFCOM_005</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q018</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -7511,24 +7511,24 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q018</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -7550,12 +7550,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q018</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q018</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q018</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -7619,24 +7619,24 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q018</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -7646,24 +7646,24 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Q031</t>
+          <t>Q018</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -7685,12 +7685,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Q031</t>
+          <t>Q018</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -7700,24 +7700,24 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Q031</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MOFCOM_006</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -7727,24 +7727,24 @@
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Q031</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>MOFCOM_005</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Q031</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -7793,12 +7793,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Q031</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -7808,19 +7808,19 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Q032</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -7847,7 +7847,7 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Q032</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -7874,12 +7874,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Q032</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Q032</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -7916,24 +7916,24 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Q032</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -7943,24 +7943,24 @@
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Q033</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -7970,24 +7970,24 @@
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Q033</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MOFCOM_005</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -8009,12 +8009,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Q033</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -8036,12 +8036,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Q033</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Q034</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>MOFCOM_006</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -8090,12 +8090,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Q034</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -8117,12 +8117,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Q034</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -8132,24 +8132,24 @@
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>Q034</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -8171,12 +8171,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Q034</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Q035</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -8213,24 +8213,24 @@
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Q035</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -8240,24 +8240,24 @@
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Q035</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -8279,12 +8279,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Q035</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>MOFCOM_006</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -8306,12 +8306,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>Q036</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>MOFCOM_005</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -8333,12 +8333,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Q036</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -8360,7 +8360,7 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>Q037</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
@@ -8387,7 +8387,7 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Q037</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>Q037</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -8429,24 +8429,24 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Q037</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -8456,19 +8456,19 @@
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>Q037</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Q037</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -8510,24 +8510,24 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>Q038</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -8549,12 +8549,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Q038</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MOFCOM_005</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>Q038</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MOFCOM_006</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -8591,24 +8591,24 @@
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Q038</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -8630,12 +8630,12 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>Q038</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -8657,12 +8657,12 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Q038</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -8672,24 +8672,24 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>Q039</t>
+          <t>Q022</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -8699,24 +8699,24 @@
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>Q039</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MOFCOM_006</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>Q039</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -8753,24 +8753,24 @@
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>Q039</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>MOFCOM_005</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>Q039</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -8807,24 +8807,24 @@
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Q039</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>Q040</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -8873,7 +8873,7 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>Q040</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
@@ -8900,12 +8900,12 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>Q040</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -8927,7 +8927,7 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Q040</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
@@ -8954,12 +8954,12 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>Q040</t>
+          <t>Q023</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -8969,24 +8969,24 @@
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>Q040</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>MOFCOM_006</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -8996,24 +8996,24 @@
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>Q041</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>MOFCOM_005</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -9035,12 +9035,12 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>Q041</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -9062,12 +9062,12 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>Q041</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
@@ -9089,12 +9089,12 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>Q041</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>EU_004</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>Q041</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>CNGOV_001</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -9131,24 +9131,24 @@
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>Q041</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>MCK_001</t>
+          <t>UNCTAD_001</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -9158,24 +9158,24 @@
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>宏观风险</t>
+          <t>对外投资</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>trade_policy; supply_chain</t>
+          <t>investment_policy</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>Q042</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>CNGOV_001</t>
+          <t>IMF_001</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>Q042</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>UNCTAD_001</t>
+          <t>WEF_001</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -9212,24 +9212,24 @@
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>Q042</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>EU_004</t>
+          <t>MCK_001</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -9239,24 +9239,24 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>对外投资</t>
+          <t>宏观风险</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>investment_policy</t>
+          <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>Q042</t>
+          <t>Q026</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>IMF_001</t>
+          <t>MOFCOM_003</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -9278,32 +9278,3974 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
+          <t>Q026</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_005</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Q026</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_004</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>Q026</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_006</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Q026</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>Q026</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>IMF_001</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>Q026</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>Q026</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>Q026</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>Q026</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>MCK_001</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>Q027</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_003</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>Q027</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_006</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>Q027</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_005</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>Q027</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_004</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>Q027</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>Q027</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>Q027</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>Q027</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>IMF_001</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>Q027</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>Q027</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>MCK_001</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>Q028</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_004</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>Q028</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_005</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>Q028</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_003</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>Q028</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_006</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>Q028</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>Q028</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>Q028</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>IMF_001</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>Q028</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>Q028</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>Q028</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>MCK_001</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>Q030</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_006</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>Q030</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_005</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>Q030</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_004</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>Q030</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>Q030</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_003</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>Q030</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>Q030</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>Q030</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>Q030</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>IMF_001</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_005</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_006</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_004</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_003</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>IMF_001</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>MCK_001</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_004</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_006</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_005</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_003</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>IMF_001</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_005</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_006</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_003</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_004</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>IMF_001</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_005</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_006</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_003</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_004</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>IMF_001</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_005</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_006</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_003</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_004</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>IMF_001</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_003</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_006</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_004</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_005</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_003</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_005</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_006</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_004</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>IMF_001</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>MCK_001</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_006</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_003</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_005</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_004</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D303" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E303" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D306" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E306" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>IMF_001</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>MCK_001</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_003</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_005</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_004</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_006</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D315" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E315" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>IMF_001</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D316" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>MCK_001</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D317" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E317" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D318" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_006</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D319" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E319" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_003</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D320" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_004</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D321" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_005</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D322" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D323" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D324" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D325" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E325" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>IMF_001</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D327" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>MCK_001</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D328" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E328" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D329" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E329" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_005</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D330" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E330" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_006</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D331" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E331" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_003</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D332" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_004</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D333" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E333" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D334" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E334" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D335" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E335" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>IMF_001</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D336" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E336" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D337" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E337" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>MCK_001</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D338" s="2" t="inlineStr">
+        <is>
+          <t>宏观风险</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="inlineStr">
+        <is>
+          <t>trade_policy; supply_chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
           <t>Q042</t>
         </is>
       </c>
-      <c r="B201" s="2" t="inlineStr">
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_006</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D339" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_004</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D340" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_005</t>
+        </is>
+      </c>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D341" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E341" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>CNGOV_001</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D342" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E342" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_003</t>
+        </is>
+      </c>
+      <c r="C343" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D343" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E343" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>UNCTAD_001</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D344" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E344" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>EU_004</t>
+        </is>
+      </c>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D345" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E345" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>IMF_001</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D346" s="2" t="inlineStr">
+        <is>
+          <t>对外投资</t>
+        </is>
+      </c>
+      <c r="E346" s="2" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
         <is>
           <t>WEF_001</t>
         </is>
       </c>
-      <c r="C201" s="2" t="inlineStr">
-        <is>
-          <t>F1:macro-drift</t>
-        </is>
-      </c>
-      <c r="D201" s="2" t="inlineStr">
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>F1:macro-drift</t>
+        </is>
+      </c>
+      <c r="D347" s="2" t="inlineStr">
         <is>
           <t>宏观风险</t>
         </is>
       </c>
-      <c r="E201" s="2" t="inlineStr">
+      <c r="E347" s="2" t="inlineStr">
         <is>
           <t>trade_policy; supply_chain</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E201"/>
+  <autoFilter ref="A1:E347"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
